--- a/projects/ai-core/doc/data/res_syn_pwr.xlsx
+++ b/projects/ai-core/doc/data/res_syn_pwr.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Dynamic Power — Baseline (top_NxN) vs Square (top_NxN_sqr), ASAP7 RVT/TT, VCD-annotated</t>
+          <t>Dynamic Power — Baseline (top_NxN) vs Square (top_NxN_sqr), ASAP7 RVT/TT, VCD-annotated, 100 vectors/mode</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.00546</v>
+        <v>0.0012</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.005459</v>
+        <v>0.001194</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>4.15e-06</v>
+        <v>4.18e-06</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.00546</v>
+        <v>0.0012</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>0.00546</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="6">
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.09889999999999999</v>
+        <v>0.09485</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.09875</v>
+        <v>0.09475</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.00015</v>
+        <v>0.000152</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.7911999999999999</v>
+        <v>0.7588</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1.5824</v>
+        <v>1.5176</v>
       </c>
     </row>
     <row r="7">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.1058</v>
+        <v>0.10455</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.000201</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.848</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1.696</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="8">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.63275</v>
+        <v>0.6407499999999999</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.63075</v>
+        <v>0.639</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.0017275</v>
+        <v>0.00173</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>40.496</v>
+        <v>41.008</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>161.984</v>
+        <v>164.032</v>
       </c>
     </row>
     <row r="9">
@@ -739,7 +739,7 @@
         <v>0.00591</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.005916</v>
+        <v>0.005915</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>2.41e-07</v>
@@ -766,19 +766,19 @@
         </is>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.0001053580000014154</v>
+        <v>1.416600000064133e-06</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.0001039699999989385</v>
+        <v>-6.505213034913027e-16</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>1.418880000000406e-06</v>
+        <v>1.416599999999759e-06</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.0001053580000014154</v>
+        <v>1.416600000064133e-06</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.0001053580000014154</v>
+        <v>1.416600000064133e-06</v>
       </c>
     </row>
     <row r="12">
@@ -793,10 +793,10 @@
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="12" t="n">
-        <v>43.56652535800001</v>
+        <v>44.0337614166</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>170.781885358</v>
+        <v>172.7447214166</v>
       </c>
     </row>
     <row r="13">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.009010000000000001</v>
+        <v>0.00167</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.009003999999999998</v>
+        <v>0.001664</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>4.52e-06</v>
+        <v>4.56e-06</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>0.009010000000000001</v>
+        <v>0.00167</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.009010000000000001</v>
+        <v>0.00167</v>
       </c>
     </row>
     <row r="15">
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>8.81e-05</v>
+        <v>1.07e-05</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>8.549999999999999e-05</v>
+        <v>8.1e-06</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>2.6e-06</v>
+        <v>2.61e-06</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.81e-05</v>
+        <v>1.07e-05</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>8.81e-05</v>
+        <v>1.07e-05</v>
       </c>
     </row>
     <row r="16">
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.1285</v>
+        <v>0.124</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.12845</v>
+        <v>0.12395</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.0001565</v>
+        <v>0.000158</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>1.028</v>
+        <v>0.992</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>2.056</v>
+        <v>1.984</v>
       </c>
     </row>
     <row r="17">
@@ -918,19 +918,19 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0.1045</v>
+        <v>0.103</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.1045</v>
+        <v>0.10305</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.000161</v>
+        <v>0.000162</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.836</v>
+        <v>0.824</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1.672</v>
+        <v>1.648</v>
       </c>
     </row>
     <row r="18">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0.3745</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.3735</v>
+        <v>0.369</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.000927</v>
+        <v>0.000926</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>2.996</v>
+        <v>2.956</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>5.992</v>
+        <v>5.912000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -978,19 +978,19 @@
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>0.35</v>
+        <v>0.346</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.349</v>
+        <v>0.345</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.0008405</v>
+        <v>0.000839</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>2.8</v>
+        <v>2.768</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>5.6</v>
+        <v>5.536</v>
       </c>
     </row>
     <row r="20">
@@ -1008,19 +1008,19 @@
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0.513</v>
+        <v>0.502</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.5120000000000001</v>
+        <v>0.50075</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0.00152</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>32.832</v>
+        <v>32.128</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>131.328</v>
+        <v>128.512</v>
       </c>
     </row>
     <row r="21">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.001677378000002235</v>
+        <v>0.001289991400007899</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.001673188700002451</v>
+        <v>0.001285621109998894</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>4.174519999998943e-06</v>
+        <v>4.187669999981635e-06</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>0.001677378000002235</v>
+        <v>0.001289991400007899</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0.001677378000002235</v>
+        <v>0.001289991400007899</v>
       </c>
     </row>
     <row r="24">
@@ -1125,10 +1125,10 @@
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="12" t="n">
-        <v>42.00197547800001</v>
+        <v>41.17017069140001</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>152.178775478</v>
+        <v>149.1149706914</v>
       </c>
     </row>
     <row r="26">
@@ -1143,10 +1143,10 @@
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="13" t="n">
-        <v>0.964088256588204</v>
+        <v>0.9349682917589578</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.891070942090823</v>
+        <v>0.8632099983639251</v>
       </c>
     </row>
     <row r="27">
@@ -1161,10 +1161,10 @@
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="14" t="n">
-        <v>-0.03591174341179604</v>
+        <v>-0.06503170824104221</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>-0.108929057909177</v>
+        <v>-0.1367900016360749</v>
       </c>
     </row>
   </sheetData>

--- a/projects/ai-core/doc/data/res_syn_pwr.xlsx
+++ b/projects/ai-core/doc/data/res_syn_pwr.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="48">
   <si>
-    <t xml:space="preserve">Dynamic Power — Baseline / Square / BFP / Square-BFP (top_NxN[_sqr][_bfp]), ASAP7 RVT/TT, VCD-annotated, 100 vectors, operand isolation</t>
+    <t xml:space="preserve">Dynamic Power — Baseline / Square / BFP / Square-BFP, ASAP7 RVT/TT, VCD-annotated, 100 vectors, operand isolation</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -418,12 +418,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:I58"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="0" width="26.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="0" width="22.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/projects/ai-core/doc/data/res_syn_pwr.xlsx
+++ b/projects/ai-core/doc/data/res_syn_pwr.xlsx
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="48">
-  <si>
-    <t xml:space="preserve">Dynamic Power — Baseline / Square / BFP / Square-BFP, ASAP7 RVT/TT, VCD-annotated, 100 vectors, operand isolation</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="54">
+  <si>
+    <t xml:space="preserve">Dynamic Power — Baseline / Square / BFP / Square-BFP / Bit-Plane BFP, ASAP7 RVT/TT, VCD-annotated, 100 vectors, operand isolation</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -155,6 +155,18 @@
     <t xml:space="preserve">Square-BFP total </t>
   </si>
   <si>
+    <t xml:space="preserve">Bit-Plane BFP — top_NxN_bpl_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disp_array_b_bpl_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pe_bpl_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bit-Plane BFP total </t>
+  </si>
+  <si>
     <t xml:space="preserve">Square / Baseline (× total power) </t>
   </si>
   <si>
@@ -165,6 +177,12 @@
   </si>
   <si>
     <t xml:space="preserve">Square-BFP / BFP (× total power) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bit-Plane BFP / Baseline (× total power) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bit-Plane BFP / BFP (× total power) </t>
   </si>
 </sst>
 </file>
@@ -296,6 +314,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -334,10 +356,6 @@
     </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -417,1261 +435,1564 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:I58"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:I71"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="0" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="1" width="22.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+    <row r="4" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="n">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>0.00127</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>0.00126</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="8" t="n">
         <v>4E-006</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="9" t="n">
         <v>0.0013</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="n">
+    <row r="6" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>0.101</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>0.10065</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>0.000126</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>0.808</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <v>1.616</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="n">
+    <row r="7" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>0.09975</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>0.0996</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="8" t="n">
         <v>0.000182</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <v>0.798</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="9" t="n">
         <v>1.596</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="n">
+    <row r="8" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>0.68225</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>0.6805</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>0.00176</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <v>43.664</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="9" t="n">
         <v>174.656</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="n">
+    <row r="9" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>0.0208</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>0.02081</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="n">
         <v>1.3312</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="9" t="n">
         <v>5.3248</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="n">
+    <row r="10" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>0.00591</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>0.00592</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9" t="n">
         <v>0.0946</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I10" s="9" t="n">
         <v>0.1891</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="n">
+    <row r="11" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>0.00139</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="F11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9" t="n">
         <v>0.0014</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="9" t="n">
         <v>0.0014</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9" t="s">
+    <row r="12" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10" t="n">
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="11" t="n">
         <v>46.698</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="11" t="n">
         <v>183.385</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+    <row r="13" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="n">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>0.00177</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>0.00177</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="8" t="n">
         <v>5E-006</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="9" t="n">
         <v>0.0018</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="9" t="n">
         <v>0.0018</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="n">
+    <row r="16" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>1E-005</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>1E-005</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="8" t="n">
         <v>2E-006</v>
       </c>
-      <c r="H16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="n">
+      <c r="H16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>0.123</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>0.12325</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="8" t="n">
         <v>0.00014</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="9" t="n">
         <v>0.984</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="9" t="n">
         <v>1.968</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="n">
+    <row r="18" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>0.107</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>0.10655</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="8" t="n">
         <v>0.000154</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="9" t="n">
         <v>0.856</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="9" t="n">
         <v>1.712</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="n">
+    <row r="19" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>0.399</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="8" t="n">
         <v>0.000973</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="9" t="n">
         <v>6.4</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="n">
+    <row r="20" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>0.365</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>0.364</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="8" t="n">
         <v>0.000869</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="9" t="n">
         <v>2.92</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="9" t="n">
         <v>5.84</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="n">
+    <row r="21" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>0.517</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>0.51525</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="8" t="n">
         <v>0.00156</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <v>33.088</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="9" t="n">
         <v>132.352</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="n">
+    <row r="22" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>0.0197</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>0.01971</v>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8" t="n">
+      <c r="G22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9" t="n">
         <v>1.2608</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="9" t="n">
         <v>5.0432</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="n">
+    <row r="23" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>0.0149</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>0.01491</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8" t="n">
+      <c r="G23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9" t="n">
         <v>0.2384</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="9" t="n">
         <v>0.4768</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="n">
+    <row r="24" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>0.00182</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>0.00317</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8" t="n">
+      <c r="G24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9" t="n">
         <v>0.0018</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I24" s="9" t="n">
         <v>0.0018</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="9" t="s">
+    <row r="25" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="10" t="n">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="11" t="n">
         <v>42.551</v>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="11" t="n">
         <v>153.796</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3" t="s">
+    <row r="26" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0"/>
+      <c r="C26" s="0"/>
+      <c r="D26" s="0"/>
+      <c r="E26" s="0"/>
+      <c r="F26" s="0"/>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+      <c r="I26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4" t="n">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>0.00136</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>0.00136</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="8" t="n">
         <v>4E-006</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="9" t="n">
         <v>0.0014</v>
       </c>
-      <c r="I28" s="8" t="n">
+      <c r="I28" s="9" t="n">
         <v>0.0014</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4" t="n">
+    <row r="29" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>0.102</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>0.1014</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="8" t="n">
         <v>0.000126</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="9" t="n">
         <v>0.816</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I29" s="9" t="n">
         <v>1.632</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="n">
+    <row r="30" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>0.101</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>0.101</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="8" t="n">
         <v>0.000182</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H30" s="9" t="n">
         <v>0.808</v>
       </c>
-      <c r="I30" s="8" t="n">
+      <c r="I30" s="9" t="n">
         <v>1.616</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4" t="n">
+    <row r="31" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>0.0138</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>0.01375</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="8" t="n">
         <v>2.9E-005</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="9" t="n">
         <v>0.1104</v>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="I31" s="9" t="n">
         <v>0.2208</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="n">
+    <row r="32" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>0.0161</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>0.01606</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="8" t="n">
         <v>4.8E-005</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="9" t="n">
         <v>0.1288</v>
       </c>
-      <c r="I32" s="8" t="n">
+      <c r="I32" s="9" t="n">
         <v>0.2576</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="n">
+    <row r="33" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>0.9185</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>0.9155</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="8" t="n">
         <v>0.00247</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="9" t="n">
         <v>58.784</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" s="9" t="n">
         <v>235.136</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="n">
+    <row r="34" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>0.0261</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>0.02611</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="8" t="n">
+      <c r="G34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9" t="n">
         <v>1.6704</v>
       </c>
-      <c r="I34" s="8" t="n">
+      <c r="I34" s="9" t="n">
         <v>6.6816</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4" t="n">
+    <row r="35" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>0.00673</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="7" t="n">
         <v>0.00673</v>
       </c>
-      <c r="G35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="8" t="n">
+      <c r="G35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="9" t="n">
         <v>0.1077</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I35" s="9" t="n">
         <v>0.2154</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4" t="n">
+    <row r="36" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="6" t="n">
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
         <v>0.00086</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="8" t="n">
         <v>4.5E-005</v>
       </c>
-      <c r="H36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="9" t="s">
+      <c r="H36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="10" t="n">
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="11" t="n">
         <v>62.427</v>
       </c>
-      <c r="I37" s="10" t="n">
+      <c r="I37" s="11" t="n">
         <v>245.761</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="3" t="s">
+    <row r="38" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0"/>
+      <c r="C38" s="0"/>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0"/>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+      <c r="I38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-    </row>
-    <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4" t="n">
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>0.00162</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>0.00162</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="8" t="n">
         <v>5E-006</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="9" t="n">
         <v>0.0016</v>
       </c>
-      <c r="I40" s="8" t="n">
+      <c r="I40" s="9" t="n">
         <v>0.0016</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="n">
+    <row r="41" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="7" t="n">
         <v>2E-005</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>2E-005</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="8" t="n">
         <v>2E-006</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4" t="n">
+      <c r="H41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>0.1225</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="7" t="n">
         <v>0.1224</v>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="8" t="n">
         <v>0.00014</v>
       </c>
-      <c r="H42" s="8" t="n">
+      <c r="H42" s="9" t="n">
         <v>0.98</v>
       </c>
-      <c r="I42" s="8" t="n">
+      <c r="I42" s="9" t="n">
         <v>1.96</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="4" t="n">
+    <row r="43" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="7" t="n">
         <v>0.108</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="7" t="n">
         <v>0.1077</v>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="8" t="n">
         <v>0.000154</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="9" t="n">
         <v>0.864</v>
       </c>
-      <c r="I43" s="8" t="n">
+      <c r="I43" s="9" t="n">
         <v>1.728</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4" t="n">
+    <row r="44" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>0.0102</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>0.01019</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="8" t="n">
         <v>2.3E-005</v>
       </c>
-      <c r="H44" s="8" t="n">
+      <c r="H44" s="9" t="n">
         <v>0.0816</v>
       </c>
-      <c r="I44" s="8" t="n">
+      <c r="I44" s="9" t="n">
         <v>0.1632</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="4" t="n">
+    <row r="45" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>0.01665</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>0.01658</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="8" t="n">
         <v>4.1E-005</v>
       </c>
-      <c r="H45" s="8" t="n">
+      <c r="H45" s="9" t="n">
         <v>0.1332</v>
       </c>
-      <c r="I45" s="8" t="n">
+      <c r="I45" s="9" t="n">
         <v>0.2664</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4" t="n">
+    <row r="46" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>0.2905</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="8" t="n">
         <v>0.000641</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="9" t="n">
         <v>2.324</v>
       </c>
-      <c r="I46" s="8" t="n">
+      <c r="I46" s="9" t="n">
         <v>4.648</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4" t="n">
+    <row r="47" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>0.272</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="7" t="n">
         <v>0.2715</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="8" t="n">
         <v>0.000562</v>
       </c>
-      <c r="H47" s="8" t="n">
+      <c r="H47" s="9" t="n">
         <v>2.176</v>
       </c>
-      <c r="I47" s="8" t="n">
+      <c r="I47" s="9" t="n">
         <v>4.352</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="4" t="n">
+    <row r="48" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="7" t="n">
         <v>0.81775</v>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="8" t="n">
         <v>0.0024</v>
       </c>
-      <c r="H48" s="8" t="n">
+      <c r="H48" s="9" t="n">
         <v>52.48</v>
       </c>
-      <c r="I48" s="8" t="n">
+      <c r="I48" s="9" t="n">
         <v>209.92</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="4" t="n">
+    <row r="49" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>0.0262</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="7" t="n">
         <v>0.02611</v>
       </c>
-      <c r="G49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="8" t="n">
+      <c r="G49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9" t="n">
         <v>1.6768</v>
       </c>
-      <c r="I49" s="8" t="n">
+      <c r="I49" s="9" t="n">
         <v>6.7072</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="4" t="n">
+    <row r="50" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>0.00673</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="7" t="n">
         <v>0.00673</v>
       </c>
-      <c r="G50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="8" t="n">
+      <c r="G50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9" t="n">
         <v>0.1077</v>
       </c>
-      <c r="I50" s="8" t="n">
+      <c r="I50" s="9" t="n">
         <v>0.2154</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="4" t="n">
+    <row r="51" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="9" t="s">
+      <c r="E51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="10" t="n">
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="11" t="n">
         <v>60.825</v>
       </c>
-      <c r="I52" s="10" t="n">
+      <c r="I52" s="11" t="n">
         <v>229.962</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-    </row>
-    <row r="54" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="9" t="s">
+    <row r="53" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="0"/>
+      <c r="C53" s="0"/>
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0"/>
+      <c r="G53" s="0"/>
+      <c r="H53" s="0"/>
+      <c r="I53" s="0"/>
+    </row>
+    <row r="54" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="10" t="n">
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>0.00137</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>4E-006</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>0.0014</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0.1219</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>0.000126</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="I56" s="9" t="n">
+        <v>1.952</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>0.000264</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="I57" s="9" t="n">
+        <v>2.376</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.01366</v>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>2.9E-005</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="I58" s="9" t="n">
+        <v>0.2192</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>4.8E-005</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I59" s="9" t="n">
+        <v>0.2584</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>58.048</v>
+      </c>
+      <c r="I60" s="9" t="n">
+        <v>232.192</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B61" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0.02621</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>1.6768</v>
+      </c>
+      <c r="I61" s="9" t="n">
+        <v>6.7072</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B62" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0.00673</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0.00673</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="I62" s="9" t="n">
+        <v>0.2154</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B63" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B64" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="11" t="n">
+        <v>62.237</v>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>243.922</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B65" s="0"/>
+      <c r="C65" s="0"/>
+      <c r="D65" s="0"/>
+      <c r="E65" s="0"/>
+      <c r="F65" s="0"/>
+      <c r="G65" s="0"/>
+      <c r="H65" s="0"/>
+      <c r="I65" s="0"/>
+    </row>
+    <row r="66" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B66" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="11" t="n">
         <v>0.9112</v>
       </c>
-      <c r="I54" s="10" t="n">
+      <c r="I66" s="11" t="n">
         <v>0.8387</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="10" t="n">
+    <row r="67" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B67" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="11" t="n">
         <v>1.3368</v>
       </c>
-      <c r="I55" s="10" t="n">
+      <c r="I67" s="11" t="n">
         <v>1.3401</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="10" t="n">
+    <row r="68" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B68" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="11" t="n">
         <v>1.3025</v>
       </c>
-      <c r="I56" s="10" t="n">
+      <c r="I68" s="11" t="n">
         <v>1.254</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="10" t="n">
+    <row r="69" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="11" t="n">
         <v>0.9743</v>
       </c>
-      <c r="I57" s="10" t="n">
+      <c r="I69" s="11" t="n">
         <v>0.9357</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B70" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="11" t="n">
+        <v>1.3327</v>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>1.3301</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B71" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="11" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="I71" s="11" t="n">
+        <v>0.9925</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="17">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B12:G12"/>
@@ -1681,10 +2002,14 @@
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
